--- a/dist/downloads/model-documents/openbmb-voxcpm1.5.xlsx
+++ b/dist/downloads/model-documents/openbmb-voxcpm1.5.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="R46cf5b8d53a14e7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="R294e304231034434"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="R4f295209558d44a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="R1e37eaf55e0e4476"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1061,7 +1061,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD6" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" hidden="0" customHeight="1">
@@ -2257,7 +2257,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD19" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="24" hidden="0" customHeight="1">
@@ -3453,7 +3453,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="24" hidden="0" customHeight="1">
@@ -4649,7 +4649,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="24" hidden="0" customHeight="1">
@@ -5845,7 +5845,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD58" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="24" hidden="0" customHeight="1">
@@ -7041,7 +7041,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD71" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="24" hidden="0" customHeight="1">
@@ -8237,7 +8237,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD84" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="24" hidden="0" customHeight="1">
@@ -9433,7 +9433,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD97" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="24" hidden="0" customHeight="1">
@@ -10629,7 +10629,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD110" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="24" hidden="0" customHeight="1">
@@ -11825,7 +11825,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD123" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="24" hidden="0" customHeight="1">
@@ -13021,7 +13021,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD136" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="24" hidden="0" customHeight="1">
@@ -14217,7 +14217,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD149" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="24" hidden="0" customHeight="1">
@@ -15413,7 +15413,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD162" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="24" hidden="0" customHeight="1">
@@ -16609,7 +16609,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD175" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="24" hidden="0" customHeight="1">
@@ -17805,7 +17805,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD188" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="24" hidden="0" customHeight="1">
@@ -19001,7 +19001,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD201" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="24" hidden="0" customHeight="1">
@@ -20197,7 +20197,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD214" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="24" hidden="0" customHeight="1">
@@ -21393,7 +21393,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD227" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="24" hidden="0" customHeight="1">
@@ -22589,7 +22589,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD240" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="24" hidden="0" customHeight="1">
@@ -23785,7 +23785,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD253" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="254" ht="24" hidden="0" customHeight="1">
@@ -24981,7 +24981,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD266" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="24" hidden="0" customHeight="1">
@@ -26177,7 +26177,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD279" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="24" hidden="0" customHeight="1">
@@ -27373,7 +27373,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD292" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="293" ht="24" hidden="0" customHeight="1">
@@ -28569,7 +28569,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD305" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="306" ht="24" hidden="0" customHeight="1">
@@ -29328,10 +29328,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G314" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H314" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I314" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -29394,7 +29394,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC314" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD314" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -29420,10 +29420,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G315" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H315" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I315" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -29486,7 +29486,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC315" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD315" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -29512,10 +29512,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G316" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H316" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I316" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -29578,7 +29578,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC316" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD316" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -29604,10 +29604,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G317" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H317" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I317" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -29670,7 +29670,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC317" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD317" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -29696,10 +29696,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G318" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H318" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I318" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -29762,7 +29762,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC318" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD318" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -29788,10 +29788,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G319" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H319" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I319" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -29854,7 +29854,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC319" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD319" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -29880,10 +29880,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G320" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H320" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I320" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -29946,7 +29946,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC320" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD320" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -29972,10 +29972,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G321" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H321" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I321" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -30038,7 +30038,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC321" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD321" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -30064,10 +30064,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G322" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H322" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I322" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -30130,7 +30130,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC322" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD322" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -30156,10 +30156,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G323" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H323" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I323" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -30222,7 +30222,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC323" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD323" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -30248,10 +30248,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G324" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H324" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I324" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -30314,7 +30314,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC324" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD324" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -30340,10 +30340,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G325" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H325" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I325" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -30406,7 +30406,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC325" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD325" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -30432,10 +30432,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G326" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H326" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I326" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -30498,7 +30498,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC326" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD326" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -30524,10 +30524,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G327" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H327" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I327" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -30590,7 +30590,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC327" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD327" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -30616,10 +30616,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G328" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H328" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I328" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -30682,7 +30682,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC328" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD328" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -30708,10 +30708,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G329" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H329" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I329" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -30774,7 +30774,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC329" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD329" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -30800,10 +30800,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G330" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H330" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I330" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -30866,7 +30866,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC330" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD330" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -30892,10 +30892,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G331" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H331" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I331" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -30958,7 +30958,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC331" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD331" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -30984,10 +30984,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G332" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H332" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I332" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -31050,7 +31050,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC332" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD332" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -31076,10 +31076,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G333" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H333" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I333" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -31142,7 +31142,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC333" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD333" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -31168,10 +31168,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G334" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H334" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I334" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -31234,7 +31234,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC334" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD334" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -31260,10 +31260,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G335" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H335" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I335" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -31326,7 +31326,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC335" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD335" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -31352,10 +31352,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G336" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H336" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I336" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -31418,7 +31418,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC336" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD336" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -31444,10 +31444,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G337" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H337" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I337" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -31510,7 +31510,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC337" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD337" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -31536,10 +31536,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G338" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H338" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I338" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -31602,7 +31602,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC338" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD338" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -31628,10 +31628,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G339" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H339" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I339" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -31694,7 +31694,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC339" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD339" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -31720,10 +31720,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G340" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H340" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I340" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -31786,7 +31786,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC340" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD340" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -31812,10 +31812,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G341" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H341" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I341" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -31878,7 +31878,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC341" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD341" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -31904,10 +31904,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G342" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H342" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I342" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -31970,7 +31970,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC342" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD342" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -31996,10 +31996,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G343" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H343" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I343" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -32062,7 +32062,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC343" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD343" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -32088,10 +32088,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G344" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H344" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I344" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -32154,7 +32154,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC344" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD344" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -32180,10 +32180,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G345" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H345" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I345" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -32246,7 +32246,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC345" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD345" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -32272,10 +32272,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G346" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H346" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I346" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -32338,7 +32338,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC346" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD346" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -32364,10 +32364,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G347" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H347" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I347" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -32430,7 +32430,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC347" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD347" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -32456,10 +32456,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G348" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H348" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I348" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -32522,7 +32522,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC348" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD348" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -32548,10 +32548,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G349" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H349" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I349" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -32614,7 +32614,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC349" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD349" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -32640,10 +32640,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G350" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H350" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I350" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -32706,7 +32706,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC350" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD350" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -32732,10 +32732,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G351" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H351" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I351" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -32798,7 +32798,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC351" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD351" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -32824,10 +32824,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G352" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H352" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I352" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -32890,7 +32890,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC352" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD352" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -32916,10 +32916,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G353" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H353" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I353" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -32982,7 +32982,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC353" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD353" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -33008,10 +33008,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G354" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H354" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I354" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -33074,7 +33074,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC354" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD354" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -33100,10 +33100,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G355" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H355" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I355" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -33166,7 +33166,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC355" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD355" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -33192,10 +33192,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G356" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H356" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I356" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -33258,7 +33258,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC356" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD356" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -33284,10 +33284,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G357" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H357" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I357" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -33350,7 +33350,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC357" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD357" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -33376,10 +33376,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G358" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H358" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I358" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -33442,7 +33442,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC358" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD358" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -33468,10 +33468,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G359" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H359" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I359" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -33534,7 +33534,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC359" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD359" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -33560,10 +33560,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G360" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H360" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I360" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -33626,7 +33626,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC360" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD360" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -33652,10 +33652,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G361" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H361" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I361" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -33718,7 +33718,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC361" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD361" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -33744,10 +33744,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G362" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H362" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I362" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -33810,7 +33810,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC362" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD362" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -33836,10 +33836,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G363" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H363" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I363" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -33902,7 +33902,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC363" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD363" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -33928,10 +33928,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G364" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H364" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I364" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -33994,7 +33994,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC364" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD364" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -34020,10 +34020,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G365" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H365" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I365" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34086,7 +34086,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC365" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD365" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -34112,10 +34112,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G366" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H366" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I366" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34178,7 +34178,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC366" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD366" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -34204,10 +34204,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G367" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H367" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I367" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34270,7 +34270,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC367" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD367" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -34296,10 +34296,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G368" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H368" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I368" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34362,7 +34362,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC368" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD368" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -34388,10 +34388,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G369" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H369" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I369" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34454,7 +34454,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC369" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD369" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -34480,10 +34480,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G370" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H370" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I370" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34546,7 +34546,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC370" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD370" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -34572,10 +34572,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G371" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H371" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I371" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34638,7 +34638,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC371" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD371" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -34664,10 +34664,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G372" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H372" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I372" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34730,7 +34730,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC372" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD372" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -34756,10 +34756,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G373" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H373" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I373" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34822,7 +34822,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC373" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD373" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -34848,10 +34848,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G374" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H374" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I374" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34914,7 +34914,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC374" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD374" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -34940,10 +34940,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G375" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H375" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I375" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35006,7 +35006,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC375" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD375" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -35032,10 +35032,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G376" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H376" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I376" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35098,7 +35098,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC376" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD376" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -35124,10 +35124,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G377" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H377" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I377" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35190,7 +35190,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC377" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD377" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -35216,10 +35216,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G378" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H378" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I378" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35282,7 +35282,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC378" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD378" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -35308,10 +35308,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G379" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H379" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I379" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35374,7 +35374,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC379" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD379" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -35400,10 +35400,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G380" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H380" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I380" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35466,7 +35466,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC380" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD380" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -35492,10 +35492,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G381" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H381" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I381" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35558,7 +35558,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC381" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD381" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -35584,10 +35584,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G382" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H382" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I382" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35650,7 +35650,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC382" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD382" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -35676,10 +35676,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G383" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H383" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I383" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35742,7 +35742,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC383" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD383" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -35768,10 +35768,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G384" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H384" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I384" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35834,7 +35834,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC384" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD384" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -35860,10 +35860,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G385" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H385" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I385" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35926,7 +35926,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC385" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD385" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -35952,10 +35952,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G386" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H386" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I386" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36018,7 +36018,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC386" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD386" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -36044,10 +36044,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G387" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H387" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I387" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36110,7 +36110,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC387" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD387" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -36136,10 +36136,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G388" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H388" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I388" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36202,7 +36202,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC388" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD388" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -36228,10 +36228,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G389" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H389" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I389" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36294,7 +36294,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC389" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD389" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -36320,10 +36320,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G390" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H390" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I390" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36386,7 +36386,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC390" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD390" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -36412,10 +36412,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G391" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H391" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I391" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36478,7 +36478,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC391" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD391" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -36504,10 +36504,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G392" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H392" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I392" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36570,7 +36570,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC392" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD392" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -36596,10 +36596,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G393" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H393" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I393" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36662,7 +36662,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC393" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD393" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -36688,10 +36688,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G394" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H394" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I394" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36754,7 +36754,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC394" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD394" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -36780,10 +36780,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G395" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H395" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I395" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36846,7 +36846,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC395" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD395" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -36872,10 +36872,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G396" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H396" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I396" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36938,7 +36938,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC396" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD396" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -36964,10 +36964,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G397" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H397" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I397" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37030,7 +37030,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC397" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD397" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -37056,10 +37056,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G398" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H398" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I398" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37122,7 +37122,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC398" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD398" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -37148,10 +37148,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G399" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H399" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I399" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37214,7 +37214,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC399" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD399" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -37240,10 +37240,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G400" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H400" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I400" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37306,7 +37306,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC400" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD400" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -37332,10 +37332,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G401" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H401" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I401" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37398,7 +37398,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC401" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD401" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -37424,10 +37424,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G402" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H402" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I402" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37490,7 +37490,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC402" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD402" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -37516,10 +37516,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G403" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H403" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I403" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37582,7 +37582,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC403" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD403" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -37608,10 +37608,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G404" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H404" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I404" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37674,7 +37674,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC404" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD404" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -37700,10 +37700,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G405" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H405" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I405" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37766,7 +37766,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC405" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD405" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -37792,10 +37792,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G406" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H406" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I406" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37858,7 +37858,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC406" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD406" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -37884,10 +37884,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G407" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H407" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I407" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37950,7 +37950,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC407" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD407" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -37976,10 +37976,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G408" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H408" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I408" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38042,7 +38042,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC408" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD408" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -38068,10 +38068,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G409" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H409" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I409" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38134,7 +38134,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC409" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD409" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -38160,10 +38160,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G410" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H410" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I410" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38226,7 +38226,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC410" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD410" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -38252,10 +38252,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G411" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H411" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I411" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38318,7 +38318,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC411" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD411" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -38344,10 +38344,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G412" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H412" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I412" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38410,7 +38410,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC412" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD412" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -38436,10 +38436,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G413" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H413" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I413" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38502,7 +38502,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC413" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD413" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -38528,10 +38528,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G414" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H414" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I414" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38594,7 +38594,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC414" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD414" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -38620,10 +38620,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G415" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H415" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I415" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38686,7 +38686,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC415" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD415" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -38712,10 +38712,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G416" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H416" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I416" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38778,7 +38778,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC416" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD416" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -38804,10 +38804,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G417" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H417" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I417" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38870,7 +38870,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC417" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD417" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -38896,10 +38896,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G418" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H418" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I418" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38962,7 +38962,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC418" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD418" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -38988,10 +38988,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G419" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H419" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I419" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39054,7 +39054,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC419" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD419" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -39080,10 +39080,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G420" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H420" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I420" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39146,7 +39146,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC420" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD420" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -39172,10 +39172,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G421" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H421" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I421" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39238,7 +39238,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC421" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD421" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -39264,10 +39264,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G422" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H422" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I422" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39330,7 +39330,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC422" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD422" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -39356,10 +39356,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G423" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H423" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I423" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39422,7 +39422,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC423" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD423" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -39448,10 +39448,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G424" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H424" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I424" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39514,7 +39514,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC424" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD424" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -39540,10 +39540,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G425" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H425" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I425" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39606,7 +39606,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC425" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD425" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -39632,10 +39632,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G426" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H426" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I426" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39698,7 +39698,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC426" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD426" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -39724,10 +39724,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G427" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H427" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I427" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39790,7 +39790,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC427" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD427" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -39816,10 +39816,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G428" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H428" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I428" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39882,7 +39882,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC428" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD428" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -39908,10 +39908,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G429" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H429" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I429" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39974,7 +39974,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC429" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD429" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -40000,10 +40000,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G430" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H430" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I430" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40066,7 +40066,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC430" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD430" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -40092,10 +40092,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G431" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H431" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I431" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40158,7 +40158,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC431" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD431" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -40184,10 +40184,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G432" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H432" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I432" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40250,7 +40250,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC432" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD432" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -40276,10 +40276,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G433" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H433" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I433" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40342,7 +40342,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC433" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD433" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -40368,10 +40368,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G434" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H434" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I434" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40434,7 +40434,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC434" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD434" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -40460,10 +40460,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G435" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H435" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I435" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40526,7 +40526,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC435" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD435" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -40552,10 +40552,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G436" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H436" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I436" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40618,7 +40618,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC436" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD436" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -40644,10 +40644,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G437" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H437" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I437" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40710,7 +40710,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC437" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD437" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -40736,10 +40736,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G438" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H438" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I438" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40802,7 +40802,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC438" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD438" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -40828,10 +40828,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G439" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H439" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I439" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40894,7 +40894,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC439" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD439" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -40920,10 +40920,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G440" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H440" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I440" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40986,7 +40986,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC440" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD440" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -41012,10 +41012,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G441" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H441" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I441" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41078,7 +41078,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC441" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD441" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -41104,10 +41104,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G442" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H442" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I442" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41170,7 +41170,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC442" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD442" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -41196,10 +41196,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G443" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H443" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I443" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41262,7 +41262,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC443" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD443" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -41288,10 +41288,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G444" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H444" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I444" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41354,7 +41354,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC444" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD444" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -41380,10 +41380,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G445" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H445" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I445" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41446,7 +41446,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC445" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD445" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -41472,10 +41472,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G446" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H446" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I446" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41538,7 +41538,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC446" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD446" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -41564,10 +41564,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G447" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H447" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I447" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41630,7 +41630,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC447" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD447" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -41656,10 +41656,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G448" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H448" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I448" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41722,7 +41722,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC448" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD448" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -41748,10 +41748,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G449" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H449" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I449" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41814,7 +41814,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC449" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD449" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -41840,10 +41840,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G450" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H450" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I450" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41906,7 +41906,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC450" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD450" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -41932,10 +41932,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G451" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H451" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I451" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41998,7 +41998,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC451" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD451" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -42024,10 +42024,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G452" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H452" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I452" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42090,7 +42090,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC452" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD452" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -42116,10 +42116,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G453" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H453" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I453" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42182,7 +42182,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC453" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD453" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -42208,10 +42208,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G454" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H454" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I454" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42274,7 +42274,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC454" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD454" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -42300,10 +42300,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G455" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H455" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I455" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42366,7 +42366,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC455" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD455" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -42392,10 +42392,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G456" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H456" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I456" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42458,7 +42458,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC456" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD456" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -42484,10 +42484,10 @@
         <x:v>[B,L_mod,1024]</x:v>
       </x:c>
       <x:c r="G457" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_mod；模态独立长度</x:v>
       </x:c>
       <x:c r="H457" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_mod由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I457" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42550,7 +42550,7 @@
         <x:v>https://huggingface.co/openbmb/VoxCPM1.5/resolve/8cdc403854cda0e3af12252d27da038fda5982ac/config.json</x:v>
       </x:c>
       <x:c r="AC457" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD457" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -42803,7 +42803,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="28" t="n">
-        <x:f>IF(ISNUMBER(C6),IF(AND(C20&gt;=1,MOD(C6,C20)=0),C6/C20,"未核验"),"未核验")</x:f>
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,IF(ISNUMBER(C6),IF(MOD(C6,C20)=0,C6/C20,"未核验"),"未核验"),"未核验"),"未核验"),"未核验")</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="D7" s="28" t="str">
@@ -43067,7 +43067,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="28"/>
-      <x:c r="E20" s="28"/>
+      <x:c r="E20" s="28" t="str">
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="28" t="str">
@@ -43080,7 +43083,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D21" s="28"/>
-      <x:c r="E21" s="28"/>
+      <x:c r="E21" s="28" t="str">
+        <x:f>IF(ISNUMBER(C21),IF(C21&gt;=1,IF(MOD(C21,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="28" t="str">
@@ -43813,8 +43819,8 @@
       <x:c r="E79" s="28"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
-    <x:dataValidation type="whole" operator="between" sqref="C3:C4">
+  <x:dataValidations count="3">
+    <x:dataValidation type="whole" operator="between" sqref="C3">
       <x:formula1>1</x:formula1>
       <x:formula2>16</x:formula2>
     </x:dataValidation>
@@ -43822,6 +43828,9 @@
       <x:formula1>1</x:formula1>
       <x:formula2>8</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="whole" operator="greaterThanOrEqual" sqref="C20:C21">
+      <x:formula1>1</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
